--- a/www/download/COUNTRY.SWE.zdW16.xlsx
+++ b/www/download/COUNTRY.SWE.zdW16.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>Suécia</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Zero depreciation</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -847,1848 +852,3409 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.064</t>
+          <t>9.13116840460841</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.061</t>
+          <t>10.3117555968073</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.067</t>
+          <t>9.70666648213052</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.083</t>
+          <t>8.06750671368279</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.095</t>
+          <t>7.33729581156151</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.097</t>
+          <t>7.44962203265104</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.101</t>
+          <t>7.36707877946249</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.117</t>
+          <t>6.75096361333928</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>6.51703543298493</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.121</t>
+          <t>7.60913469791038</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>0.133</t>
+          <t>7.19279594366375</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>0.152</t>
+          <t>6.48752411302059</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>6.77125936302157</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>6.51308829461491</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6.83980225206159</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>4.301</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>4.396</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>4.39</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>4.376</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>4.348</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>4.356</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>4.434</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>4.53</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>4.567</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>4.462</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>4.506</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>4.595</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>4.628</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>4.672</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>4.75</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>4.025</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>4.126</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>4.136</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>4.131</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>4.093</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>4.109</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>4.176</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>4.271</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>4.324</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>4.209</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>4.247</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>4.353</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>4.394</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>4.442</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>4.518</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>7027.639</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>7088.821</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>6972.452</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>6866.041</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>6936.24</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>6919.239</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>7032.312</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>7240.66</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>7337.915</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>7133.265</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>7321.502</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>7452.903</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>7444.999</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>7487.874</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>7614.259</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>6528.524</t>
+          <t>8146413855.63023</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>6608.288</t>
+          <t>7703714104.50408</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>6526.947</t>
+          <t>7538978611.5376</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>6447.867</t>
+          <t>7704689452.92551</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>6494.826</t>
+          <t>8185163366.66737</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>6497.448</t>
+          <t>8271082588.37756</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>6592.548</t>
+          <t>8285021456.79083</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>6800.544</t>
+          <t>8379042946.8786</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>6920.436</t>
+          <t>8448277981.26453</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>6706.98</t>
+          <t>7538292031.82342</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>6885.54</t>
+          <t>7871744797.62031</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>7045.836</t>
+          <t>8443124307.34255</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>7049.849</t>
+          <t>8078731838.39138</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>7092.37</t>
+          <t>8069820990.38977</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>7215.88</t>
+          <t>8026465010.00051</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>3566462086.90816</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>3583394075.39151</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>3655658203.06033</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>3874142963.08788</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>4129071132.85538</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>4003302176.80594</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>3984046720.75958</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>3983174773.04794</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>3962722422.15929</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>3566389084.30284</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>3271998008.89845</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>3711731350.49528</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>3473874209.29322</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>3701848735.5306</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>3695880739.29312</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>987950.286684156</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>993295.303551362</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>908692.399083692</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>766555.365710549</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>706841.643821006</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>686813.075614697</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>625154.552565594</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>533356.325783237</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>497154.544407166</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>577111.489769061</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>531696.347363435</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>492335.613626545</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>494311.95574091</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>486876.251663723</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>492300.63688232</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>36013.6220517813</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>35652.8104655652</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>35548.2700931121</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>38110.1468241652</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>42249.2017544349</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>45396.3330003546</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>48214.0870018833</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>55443.3991797459</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>61394.8530557094</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>54107.00164344</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>60657.5177218178</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>66204.1612967583</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>64378.1278881126</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>63989.1826808153</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>64959.4409399325</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>73898.8881480779</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>68859.7308296655</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>67882.922621989</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>75528.6209938562</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>88424.6588822964</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>96508.5237454218</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>102153.565911515</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>115893.054506386</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>127444.572823811</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>103925.638528</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>119898.816007723</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>137118.19419754</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>128158.500374726</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>127274.853339103</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>127032.989464017</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>0.830532286874724</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>0.844142134793813</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>0.785436886450699</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0.664333779479509</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>0.572950862560858</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>0.623022123497064</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>0.654736618837415</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>0.707317501108845</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>0.746384243645573</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>0.880608044007368</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>1.104383921162</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>0.898261305754209</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>1.02939098403172</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>0.915899461781607</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>0.952411484300255</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>9.13116840460841</t>
+          <t>886.07753712004</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>10.3117555968073</t>
+          <t>868.491050749275</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>9.70666648213052</t>
+          <t>883.863201900468</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>8.06750671368279</t>
+          <t>937.822068043545</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>7.33729581156151</t>
+          <t>1008.81288366855</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>7.44962203265104</t>
+          <t>974.276509322449</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>7.36707877946249</t>
+          <t>954.034176427103</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>6.75096361333928</t>
+          <t>932.609406005137</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>6.51703543298493</t>
+          <t>916.448293746366</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>7.60913469791038</t>
+          <t>847.324562675895</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>7.19279594366375</t>
+          <t>770.425714362716</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>6.48752411302059</t>
+          <t>852.683517228412</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>6.77125936302157</t>
+          <t>790.594949770875</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>6.51308829461491</t>
+          <t>833.374321371139</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>6.83980225206159</t>
+          <t>818.034692185285</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.117</t>
+          <t>6233287727.45646</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.111</t>
+          <t>5918377721.53124</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.122</t>
+          <t>6301149622.38444</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.152</t>
+          <t>7301137499.462</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.173</t>
+          <t>8582776676.71292</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.176</t>
+          <t>7945596896.28234</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.186</t>
+          <t>8109698249.06157</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.219</t>
+          <t>7987921167.06161</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.238</t>
+          <t>7530818569.39224</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.204</t>
+          <t>6289458966.92204</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>0.223</t>
+          <t>6213384116.80662</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>0.261</t>
+          <t>6789010512.48531</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>6310534447.3858</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>0.278</t>
+          <t>6607834353.77609</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>0.275</t>
+          <t>6101634162.53865</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.125</t>
+          <t>5611877221.01538</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.118</t>
+          <t>5186412416.34452</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.129</t>
+          <t>5551754697.16505</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.161</t>
+          <t>6351039154.585</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.183</t>
+          <t>7295709404.21798</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0.186</t>
+          <t>6506743045.90499</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0.198</t>
+          <t>6543195913.88113</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0.232</t>
+          <t>6328488187.46785</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>0.251</t>
+          <t>5869760496.74163</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>0.216</t>
+          <t>4838952477.14805</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>0.236</t>
+          <t>4950963646.13854</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>0.275</t>
+          <t>5341071101.14112</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>0.273</t>
+          <t>4920294335.66912</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>0.292</t>
+          <t>4906648050.31462</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>0.289</t>
+          <t>4692744721.05178</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.662</t>
+          <t>621410506.441079</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.637</t>
+          <t>731965305.186725</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.714</t>
+          <t>749394925.219393</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0.891</t>
+          <t>950098344.876996</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>1.028</t>
+          <t>1287067272.49494</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>1.058</t>
+          <t>1438853850.37735</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>1.133</t>
+          <t>1566502335.18044</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>1.326</t>
+          <t>1659432979.59376</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>1.498</t>
+          <t>1661058072.65061</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>1.352</t>
+          <t>1450506489.77398</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1.481</t>
+          <t>1262420470.66808</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>1.704</t>
+          <t>1447939411.34419</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>1.686</t>
+          <t>1390240111.71668</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>1.804</t>
+          <t>1701186303.46147</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1408889441.48687</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.473</t>
+          <t>1621.99354037267</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.436</t>
+          <t>1601.62094037809</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.473</t>
+          <t>1578.08196324952</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.583</t>
+          <t>1560.8489469862</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.678</t>
+          <t>1586.81309552895</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.705</t>
+          <t>1581.27232903383</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.765</t>
+          <t>1578.67528735632</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.895</t>
+          <t>1592.26036057129</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>0.967</t>
+          <t>1600.47086031452</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>0.777</t>
+          <t>1593.48538845331</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>0.881</t>
+          <t>1621.27148575465</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>1.026</t>
+          <t>1618.6161268091</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>0.988</t>
+          <t>1604.42626308603</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>1596.66141377758</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>1.018</t>
+          <t>1597.14032757857</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>1633.9546041165</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.212</t>
+          <t>1612.56162600216</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.233</t>
+          <t>1588.25783977186</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.293</t>
+          <t>1569.02225241587</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.338</t>
+          <t>1595.27136545358</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.343</t>
+          <t>1588.43871252655</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.371</t>
+          <t>1585.99740479867</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.431</t>
+          <t>1598.37971189367</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.459</t>
+          <t>1606.72549128245</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>1598.66978775496</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>1624.83389720287</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>0.497</t>
+          <t>1621.9592946891</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>0.481</t>
+          <t>1608.68612298387</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>0.512</t>
+          <t>1602.71272909693</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>0.507</t>
+          <t>1603.00185976312</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>109515.693015692</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>100880.89326022</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>106693.171318424</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>130680.23111025</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>158123.767070916</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>168557.507085961</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>190447.640027223</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>224410.168817592</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>246317.766453469</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>180884.567917628</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>210533.527859799</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>243286.428098638</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>233819.21729835</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>236130.662360506</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>235353.739682934</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>2254724546.1386</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>2099308176.44868</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>2056475495.94336</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>2167203935.36093</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>2363503525.77888</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>2399969384.79851</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>2447981303.50306</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>2457903149.16771</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>2505693276.97369</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>2030971244.94157</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>2189343832.41467</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>2358512510.87896</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>2278667281.69793</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>2209258083.95986</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>2201262772.74472</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>87995.9755618883</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>80903.7143575521</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>84721.7031782072</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>103015.811748425</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>121260.3511701</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>133048.569736183</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>150702.825339833</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>180580.451299983</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>202251.279091825</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>147907.62328207</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>174128.083067081</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>205869.08430262</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>196207.620185438</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>199088.997946987</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>203795.938528012</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>7027.639</t>
+          <t>5545085685.34227</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>7088.821</t>
+          <t>5174316548.92285</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>6972.452</t>
+          <t>5210683870.09756</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>6866.041</t>
+          <t>5733374628.08158</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>6936.24</t>
+          <t>6411201297.34131</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>6919.239</t>
+          <t>6383508585.09204</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>7032.312</t>
+          <t>6532966972.22422</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>7240.66</t>
+          <t>6640026905.27556</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>7337.915</t>
+          <t>6695884290.97822</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>7133.265</t>
+          <t>5512386953.70159</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>7321.502</t>
+          <t>5639281508.59205</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>7452.903</t>
+          <t>6458683715.21396</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>7444.999</t>
+          <t>5868397915.48408</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>7487.874</t>
+          <t>6110800441.79593</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>7614.259</t>
+          <t>6019403812.88036</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>6528.524</t>
+          <t>21519.7174538036</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>6608.288</t>
+          <t>19977.1789026681</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>6526.947</t>
+          <t>21971.4681402167</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>6447.867</t>
+          <t>27664.419361825</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>6494.826</t>
+          <t>36863.4159008155</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>6497.448</t>
+          <t>35508.937349778</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>6592.548</t>
+          <t>39744.8146873895</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>6800.544</t>
+          <t>43829.7175176092</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>6920.436</t>
+          <t>44066.4873616438</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>6706.98</t>
+          <t>32976.9446355578</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>6885.54</t>
+          <t>36405.4447927183</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>7045.836</t>
+          <t>37417.3437960174</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>7049.849</t>
+          <t>37611.5971129125</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>7092.37</t>
+          <t>37041.6644135192</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>7215.88</t>
+          <t>31557.8011549222</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>9731.542</t>
+          <t>-3290361139.20366</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>9199.535</t>
+          <t>-3075008372.47417</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>9040.398</t>
+          <t>-3154208374.1542</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>9358.92</t>
+          <t>-3566170692.72065</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>9974.81</t>
+          <t>-4047697771.56244</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>10125.868</t>
+          <t>-3983539200.29353</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>10208.558</t>
+          <t>-4084985668.72116</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>10259.024</t>
+          <t>-4182123756.10786</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>10438.949</t>
+          <t>-4190191014.00453</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>9289.064</t>
+          <t>-3481415708.76002</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>9576.947</t>
+          <t>-3449937676.17737</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>10331.371</t>
+          <t>-4100171204.335</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>9914.805</t>
+          <t>-3589730633.78614</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>9929.628</t>
+          <t>-3901542357.83607</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>8026.465</t>
+          <t>-3818141040.13565</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>116697.979335</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.074</t>
+          <t>107112.5107306</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>118206.515602</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.082</t>
+          <t>148282.079718</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.097</t>
+          <t>171035.36373</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.106</t>
+          <t>171490.5819</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.113</t>
+          <t>185855.603407</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.128</t>
+          <t>216771.718086</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.141</t>
+          <t>228167.852232</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.114</t>
+          <t>182354.654181</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>0.131</t>
+          <t>212758.302156</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>242185.59827</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>229795.486415</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>240471.18477</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>0.127</t>
+          <t>237965.574780558</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>3970.044</t>
+          <t>0.158908511075591</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>3988.675</t>
+          <t>0.147766225924167</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>3947.939</t>
+          <t>0.145761215510584</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>3887.624</t>
+          <t>0.147779377647861</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>3910.862</t>
+          <t>0.150067985906866</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>3890.608</t>
+          <t>0.148574847132991</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>3910.336</t>
+          <t>0.152692594944915</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>4008.546</t>
+          <t>0.149628678020327</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>4069.854</t>
+          <t>0.138691994906984</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>3924.675</t>
+          <t>0.121070130459572</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>3982.362</t>
+          <t>0.131425718343155</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>4076.556</t>
+          <t>0.130304100426266</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>4058.206</t>
+          <t>0.123220464622249</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>4057.213</t>
+          <t>0.121923648174772</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>4104.404</t>
+          <t>0.121968139349296</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>117269.535183817</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>110962.28844604</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>121982.378873636</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>151980.112674193</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>172780.705363304</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.041</t>
+          <t>175940.884786701</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>186435.19751026</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>219351.341539</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>238148.153825205</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>203967.363620203</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>222528.63388409</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>0.059</t>
+          <t>260874.542279512</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>0.057</t>
+          <t>259875.863865115</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>0.057</t>
+          <t>278349.6733697</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>0.065</t>
+          <t>275409.608291217</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>4083.848</t>
+          <t>125191.300661877</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>4076.103</t>
+          <t>118015.305087275</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>4166.124</t>
+          <t>129288.803330567</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>4430.687</t>
+          <t>160836.374917403</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>4708.223</t>
+          <t>183303.796960623</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>4586.277</t>
+          <t>186294.566558412</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>4581.653</t>
+          <t>197667.731787319</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>4554.149</t>
+          <t>232389.625702087</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>4561.278</t>
+          <t>251281.270708597</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>4132.208</t>
+          <t>215864.512905543</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>3795.893</t>
+          <t>235609.917431781</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>4299.671</t>
+          <t>274735.143898353</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>4042.077</t>
+          <t>272865.473194269</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>4300.948</t>
+          <t>291883.189070697</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>3695.881</t>
+          <t>288875.852157231</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>59.86</t>
+          <t>662040.983818531</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>62.12</t>
+          <t>636824.493535603</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>56.67</t>
+          <t>713731.644491386</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>45.53</t>
+          <t>891477.023350319</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>37.95</t>
+          <t>1028065.49717087</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>41.67</t>
+          <t>1057625.54022889</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>43.89</t>
+          <t>1133268.58628414</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>49.33</t>
+          <t>1325522.22809635</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>51.72</t>
+          <t>1498462.19943231</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>62.31</t>
+          <t>1351703.74012876</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>81.39</t>
+          <t>1481083.079584</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>63.87</t>
+          <t>1704120.48106881</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>74.41</t>
+          <t>1685527.3598538</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>64.9</t>
+          <t>1803772.91324202</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>95.24</t>
+          <t>1790168.69205463</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>compensation.emp.s.cu</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>1.233</t>
+          <t>158222.412801755</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>162403.532394248</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>1.141</t>
+          <t>163865.691069218</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>0.973</t>
+          <t>165903.100348935</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0.898</t>
+          <t>169951.686874692</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>0.885</t>
+          <t>173279.059095718</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>0.811</t>
+          <t>177476.972922383</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>0.687</t>
+          <t>184559.623889099</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>0.649</t>
+          <t>186564.82913081</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>0.753</t>
+          <t>182925.094546165</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>185594.400978376</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>0.634</t>
+          <t>192168.623968691</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>0.639</t>
+          <t>195409.085522197</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>197833.092157389</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>0.492</t>
+          <t>201381.681562191</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>148195.422609894</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>152660.489706327</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>154594.72068569</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>156610.551921125</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>159954.91135115</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>162862.904493732</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>166756.167774583</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>173858.133534969</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>176532.489298259</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>172181.173805911</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>175290.028101755</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>182505.51103579</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>186014.373117814</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>188564.717410797</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>191789.359273463</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>105203.947009622</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>94101.1519858248</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>104034.392049433</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>131741.919698078</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>154279.718540773</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>157136.552963454</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>173041.721209281</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>198336.138676614</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>207824.711731973</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>163650.948160081</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>194652.407660219</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>222053.886303647</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>207691.464414698</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>219922.574061303</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>218343.544491266</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>6528524000</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>6608288000</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>6526947000</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>6447867000</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>6494826000</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>6497448000</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>6592548000</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>6800544000</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>6920436000</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>6706980000</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>6885540000</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>7045836000</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>7049849000</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>7092370000</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>7215880000</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>7027638752.30506</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>7088820907.90552</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>6972451916.59847</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>6866041376.57185</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>6936239896.99215</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>6919239031.76567</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>7032312492.87729</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>7240660094.87832</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>7337915318.68694</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>7133264592.96264</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>7321501540.79612</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>7452902959.09643</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>7444999377.16936</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>7487873870.34087</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>7614258833.87482</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>3970044435.39375</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>3988674593.11153</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>3947939151.08072</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>3887623558.08765</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>3910861775.91776</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>3890607843.57128</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>3910335794.60349</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>4008545851.40325</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>4069853848.94016</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>3924675230.5949</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>3982362090.48572</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>4076555753.69236</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>4058206283.19629</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>4057213471.53876</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>4104403761.36511</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>4301000</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>4396000</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>4390000</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>4376000</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>4348000</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>4356000</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>4434000</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>4530000</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>4567000</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>4462000</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>4506000</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>4595000</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>4628000</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>4672000</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>4750000</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>4025000</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>4126000</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>4136000</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>4131000</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>4093000</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>4109000</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>4176000</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>4271000</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>4324000</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>4209000</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>4247000</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>4353000</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>4394000</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>4442000</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>4518000</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>7027638752.30506</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>7088820907.90552</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>6972451916.59847</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>6866041376.57185</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>6936239896.99215</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>6919239031.76567</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>7032312492.87729</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>7240660094.87832</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>7337915318.68694</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>7133264592.96264</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>7321501540.79612</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>7452902959.09643</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>7444999377.16936</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>7487873870.34087</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>7614258833.87482</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>6528524000</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>6608288000</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>6526947000</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>6447867000</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>6494826000</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>6497448000</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>6592548000</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>6800544000</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>6920436000</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>6706980000</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>6885540000</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>7045836000</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>7049849000</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>7092370000</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>7215880000</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>472785.125715</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>436496.1997214</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>472981.72865</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>582971.528112</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>677672.58636</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>704701.80207</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>765462.762275</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>895474.375005</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>966660.987216</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>776644.490232</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>881199.643092</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>1026105.259386</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>987678.354841</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>1030249.851996</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>1018189.4674441</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>230395.138155</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>212116.3600964</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>233323.19538</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>292578.170658</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>337583.65179</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>343431.253755</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>370709.317255</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>430725.616251</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>459105.828996</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>379515.592485</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>430262.047036</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>496789.030202</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>480556.789925</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>511805.763132</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>507219.250428</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>850561.488480819</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>892870.964256212</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>917082.116641746</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>927614.525124867</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>957452.129729082</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>981983.39175803</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>1015232.92599233</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>1062818.05458653</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>1113220.5433455</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>1150310.09150782</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>1166677.41751468</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>1189342.22784868</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>1224540.67711016</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>1249898.90288347</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>1283530.35807266</t>
         </is>
       </c>
     </row>
@@ -2699,7 +4265,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2722,36 +4288,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -2763,331 +4344,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3124,6 +5069,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Zero depreciation</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>zdW16</t>
